--- a/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200qsp_incorrect.xlsx
+++ b/eval/learning-curve/results/learning_curve_llama3.1-70b_ft200qsp_incorrect.xlsx
@@ -688,17 +688,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -713,7 +713,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NRTI</t>
+          <t>Tenofovir (TFV), Didanosine (ddI), Stavudine (d4T), Apricitabine (ATC), Abacavir (ABC), Lamivudine (3TC), Emtricitabine (FTC), Zidovudine (AZT)</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -738,17 +738,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tenofovir (TFV), Didanosine (ddI), Stavudine (d4T), Apricitabine (ATC), Abacavir (ABC), Lamivudine (3TC), Emtricitabine (FTC), Zidovudine (AZT)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -938,17 +938,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -963,17 +963,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Integrase, IN</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -988,17 +988,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG)</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG)</t>
+          <t>Integrase, IN</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1138,17 +1138,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Reverse transcriptase, RT</t>
+          <t>NNRTI</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NNRTI</t>
+          <t>Doravirine (DOR), Rilpivirine (RPV)</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1188,17 +1188,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Doravirine (DOR), Rilpivirine (RPV)</t>
+          <t>Reverse transcriptase, RT</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1213,17 +1213,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>NRTI, PI</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>AZT, 3TC, LPV</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1263,17 +1263,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NRTI, PI</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>AZT, 3TC, LPV</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1313,17 +1313,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>PBMC, Plasma</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PBMC, Plasma</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1363,17 +1363,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Nevirapine, Efavirenz, Etravirine, Rilpivirine, Tenofovir alafenamide</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1413,17 +1413,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Nevirapine, Efavirenz, Etravirine, Rilpivirine, Tenofovir alafenamide</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not applicable</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Integrase, IN</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB)</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -1488,17 +1488,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Not applicable</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB)</t>
+          <t>Integrase, IN</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>K03455, AF324493</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1563,17 +1563,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1588,17 +1588,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>TAF, TFV, ABC, FTC, DTG, DRV, ZDV</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>What were the GenBank accession numbers for sequenced HIV isolates?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>K03455, AF324493</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1638,17 +1638,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TAF, TFV, ABC, FTC, DTG, DRV, ZDV</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1838,17 +1838,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>EFV, DTG, TDF, 3TC</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Dolutegravir (DTG), Efavirenz (EFV)</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -1863,17 +1863,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>EFV, DTG, TDF, 3TC</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG), Efavirenz (EFV)</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -1888,17 +1888,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -1913,17 +1913,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -1938,17 +1938,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2021-2022</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -1963,17 +1963,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -1988,17 +1988,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -2013,17 +2013,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -2038,17 +2038,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2021-2022</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -2063,17 +2063,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC), cabotagravir (CAB), Lenacapavir (LEN)</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -2113,17 +2113,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -2138,17 +2138,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2016-2020</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -2163,17 +2163,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>2016-2020</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -2263,17 +2263,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>INSTI, NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>INSTI, NRTI, NNRTI</t>
+          <t>TAF, FTC, DTG, TDF, EFV, 3TC</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2313,17 +2313,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>TAF, FTC, DTG, TDF, EFV, 3TC</t>
+          <t>172</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -2438,17 +2438,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -2463,17 +2463,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>TDF,FTC,EVG</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Ritonavir, Nevirapine, Efavirenz, Etravirine, Rilpivirine, Doravirine, Amprenavir, Lopinavir, Atazanavir, Derunavir, Raltegravir, Elvitegravir, Dolutegravir, Bictegravir, Cabotegravir, Lenacapavir</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -2488,17 +2488,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TDF,FTC,EVG</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Ritonavir, Nevirapine, Efavirenz, Etravirine, Rilpivirine, Doravirine, Amprenavir, Lopinavir, Atazanavir, Derunavir, Raltegravir, Elvitegravir, Dolutegravir, Bictegravir, Cabotegravir, Lenacapavir</t>
+          <t>382</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -2563,17 +2563,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -2588,17 +2588,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -2613,17 +2613,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -2638,17 +2638,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -2663,17 +2663,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -2688,17 +2688,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -2763,17 +2763,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>8 and 10</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -2788,17 +2788,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -2813,17 +2813,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>8 and 10</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -2838,17 +2838,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E97" t="n">
@@ -2913,17 +2913,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -2938,17 +2938,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>RPV</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>NNRTI</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -3113,17 +3113,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>RPV</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NNRTI</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -3238,17 +3238,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>DRV</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -3313,17 +3313,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>DRV</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3538,17 +3538,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E125" t="n">
@@ -3563,17 +3563,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI, CAI</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN; Capsid, CA</t>
+          <t>ABC, AZT, 3TC, FTC, TDF, TFV, NVP, DLV, EFV, ETR, RPV, DOR, APV, LPV, ATV, DRV, RAL, EVG, DTG, BIC, CAB, LEN, GS-CA1, GS-6207</t>
         </is>
       </c>
       <c r="E127" t="n">
@@ -3613,17 +3613,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI, CAI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E128" t="n">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ABC, AZT, 3TC, FTC, TDF, TFV, NVP, DLV, EFV, ETR, RPV, DOR, APV, LPV, ATV, DRV, RAL, EVG, DTG, BIC, CAB, LEN, GS-CA1, GS-6207</t>
+          <t>Protease, PR; Reverse transcriptase, RT; Integrase, IN; Capsid, CA</t>
         </is>
       </c>
       <c r="E129" t="n">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -3713,17 +3713,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC)</t>
         </is>
       </c>
       <c r="E133" t="n">
@@ -3763,17 +3763,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Raltegravir (RAL), Elvitegravir(EVG), Dolutagravir (DTG), Bictegravir (BIC)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E134" t="n">
@@ -3838,17 +3838,17 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>NRTI, PI, NNRTI, INSTI</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2014-2020</t>
+          <t>Abacavir, Lamivudine, Tenofovir disoproxil fumarate, Emtricitabine, Tenofovir alafenamide, Darunavir, Rilpivirine, Elvitegravir, Dolutegravir, Raltegravir</t>
         </is>
       </c>
       <c r="E138" t="n">
@@ -3888,17 +3888,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NRTI, PI, NNRTI, INSTI</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="E139" t="n">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Abacavir, Lamivudine, Tenofovir disoproxil fumarate, Emtricitabine, Tenofovir alafenamide, Darunavir, Rilpivirine, Elvitegravir, Dolutegravir, Raltegravir</t>
+          <t>2014-2020</t>
         </is>
       </c>
       <c r="E140" t="n">
@@ -3938,17 +3938,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Integrase, IN</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E141" t="n">
@@ -3963,17 +3963,17 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E142" t="n">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Dolutegravir (DTG), Bictegravir (BIC)</t>
         </is>
       </c>
       <c r="E143" t="n">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG), Bictegravir (BIC)</t>
+          <t>Integrase, IN</t>
         </is>
       </c>
       <c r="E144" t="n">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E161" t="n">
@@ -4463,17 +4463,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E162" t="n">
@@ -4488,17 +4488,17 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>CAB, RPV</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>INSTI, NNRTI</t>
         </is>
       </c>
       <c r="E163" t="n">
@@ -4513,17 +4513,17 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>CAB, RPV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>INSTI, NNRTI</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="E164" t="n">
@@ -4588,17 +4588,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma; PBMC</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Whole Blood</t>
         </is>
       </c>
       <c r="E167" t="n">
@@ -4613,17 +4613,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Plasma; PBMC</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Whole Blood</t>
+          <t>NRTI, NNRTI, PI, INST</t>
         </is>
       </c>
       <c r="E168" t="n">
@@ -4638,17 +4638,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Lamivudine (3TC), Tenofovir (TAF), Dolutegravir (DTG)</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INST</t>
+          <t>Lamivudine (3TC), Tenofovir (TFV), Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Stavudine (D4T), Emtricitabine(FTC)</t>
         </is>
       </c>
       <c r="E169" t="n">
@@ -4663,17 +4663,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Lamivudine (3TC), Tenofovir (TAF), Dolutegravir (DTG)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Lamivudine (3TC), Tenofovir (TFV), Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Stavudine (D4T), Emtricitabine(FTC)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E170" t="n">
@@ -4738,17 +4738,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>9387</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>14969</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E173" t="n">
@@ -4763,17 +4763,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>NNRTI</t>
         </is>
       </c>
       <c r="E174" t="n">
@@ -4788,17 +4788,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>9387</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NNRTI</t>
+          <t>14969</t>
         </is>
       </c>
       <c r="E175" t="n">
@@ -4838,17 +4838,17 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>INSTI</t>
         </is>
       </c>
       <c r="E177" t="n">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E178" t="n">
@@ -4888,17 +4888,17 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>INSTI</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E179" t="n">
@@ -5038,17 +5038,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2016-2017, 2019-2020</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E185" t="n">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E186" t="n">
@@ -5088,17 +5088,17 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>2016-2017, 2019-2020</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E187" t="n">
@@ -5113,17 +5113,17 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="E188" t="n">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E189" t="n">
@@ -5163,17 +5163,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E190" t="n">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>atazanavir, fosamprenavir, indinavir, saquinavir, nelfinavir, abacavir, didanosine, emtricitabine, lamivudine, azidothymidine, stavudine, tenofovir, doravirine, etravirine, nevirapine, rilpivirine, efavirenz, etravirine</t>
         </is>
       </c>
       <c r="E191" t="n">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>atazanavir, fosamprenavir, indinavir, saquinavir, nelfinavir, abacavir, didanosine, emtricitabine, lamivudine, azidothymidine, stavudine, tenofovir, doravirine, etravirine, nevirapine, rilpivirine, efavirenz, etravirine</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E192" t="n">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E193" t="n">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="E195" t="n">
@@ -5338,17 +5338,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>LPV, DTG, RAL, ABC, 3TC</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>Lopinavir, Dolutegravir, Raltegravir</t>
         </is>
       </c>
       <c r="E197" t="n">
@@ -5363,17 +5363,17 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Botswana, South Africa, Thailand, and the U.S.</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>57</t>
         </is>
       </c>
       <c r="E198" t="n">
@@ -5388,12 +5388,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>Botswana, South Africa, Thailand, and the U.S.</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5413,17 +5413,17 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E200" t="n">
@@ -5438,17 +5438,17 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>LPV, DTG, RAL, ABC, 3TC</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Lopinavir, Dolutegravir, Raltegravir</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E201" t="n">
@@ -5513,17 +5513,17 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>INSTI, NNRTI, PI, NRTI</t>
         </is>
       </c>
       <c r="E204" t="n">
@@ -5538,17 +5538,17 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Etravirine, Dolutegravir, Darunavir, Ritonavir, Tenofovir, Lamivudine, Emtricitabine, Abacavir, Efavirenz</t>
         </is>
       </c>
       <c r="E205" t="n">
@@ -5563,17 +5563,17 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>INSTI, NNRTI, PI, NRTI</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E206" t="n">
@@ -5588,17 +5588,17 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Etravirine, Dolutegravir, Darunavir, Ritonavir, Tenofovir, Lamivudine, Emtricitabine, Abacavir, Efavirenz</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E207" t="n">
@@ -5638,17 +5638,17 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>70 or 79</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E209" t="n">
@@ -5663,17 +5663,17 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E210" t="n">
@@ -5688,17 +5688,17 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2016-2022</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E211" t="n">
@@ -5713,17 +5713,17 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>RT</t>
+          <t>NRTI, INSTI</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E212" t="n">
@@ -5738,17 +5738,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>DTG, BIC, FTC, TAF</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>NRTI, NNRTI, INST</t>
         </is>
       </c>
       <c r="E213" t="n">
@@ -5763,17 +5763,17 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>70 or 79</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E214" t="n">
@@ -5788,17 +5788,17 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E215" t="n">
@@ -5813,17 +5813,17 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>NRTI, INSTI</t>
+          <t>2016-2022</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E216" t="n">
@@ -5838,17 +5838,17 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>DTG, BIC, FTC, TAF</t>
+          <t>RT</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, INST</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E217" t="n">
@@ -5888,17 +5888,17 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E219" t="n">
@@ -5913,17 +5913,17 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>57902</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>67939</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E220" t="n">
@@ -5938,17 +5938,17 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>57902</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>67939</t>
         </is>
       </c>
       <c r="E221" t="n">
@@ -5963,17 +5963,17 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E222" t="n">
@@ -5988,17 +5988,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sanger sequencing</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -6013,17 +6013,17 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Sanger sequencing</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E224" t="n">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Protease, PR</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="E230" t="n">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>Darunavir, Lopinavir</t>
         </is>
       </c>
       <c r="E231" t="n">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Darunavir, Lopinavir</t>
+          <t>Protease, PR</t>
         </is>
       </c>
       <c r="E232" t="n">
@@ -6238,17 +6238,17 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E233" t="n">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>TPV, D4T, AZT, ETR, RPV, NVP, EFV</t>
         </is>
       </c>
       <c r="E234" t="n">
@@ -6288,17 +6288,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>TPV, D4T, AZT, ETR, RPV, NVP, EFV</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E235" t="n">
@@ -6338,17 +6338,17 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>INSTI, NRTI</t>
         </is>
       </c>
       <c r="E237" t="n">
@@ -6363,17 +6363,17 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2020-2021</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Bictegravir, Emtricitabine, Tenofovir</t>
         </is>
       </c>
       <c r="E238" t="n">
@@ -6388,17 +6388,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>RT, IN</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E239" t="n">
@@ -6413,17 +6413,17 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2020-2021</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>INSTI, NRTI</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E240" t="n">
@@ -6438,17 +6438,17 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>RT, IN</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Bictegravir, Emtricitabine, Tenofovir</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="E241" t="n">
@@ -6513,17 +6513,17 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>South America, Africa, USA, Asia, Australia, Europe</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>South America, Africa, USA</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E244" t="n">
@@ -6538,17 +6538,17 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INST</t>
         </is>
       </c>
       <c r="E245" t="n">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INST</t>
+          <t>NRTI (Tenofovir, Emtricitabine), NNRTI (Efavirenz), PI, INSTI</t>
         </is>
       </c>
       <c r="E246" t="n">
@@ -6588,17 +6588,17 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>South America, Africa, USA, Asia, Australia, Europe</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>NRTI (Tenofovir, Emtricitabine), NNRTI (Efavirenz), PI, INSTI</t>
+          <t>South America, Africa, USA</t>
         </is>
       </c>
       <c r="E247" t="n">
@@ -6613,17 +6613,17 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Serum, Plasma, DBS</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>DBS</t>
         </is>
       </c>
       <c r="E248" t="n">
@@ -6638,17 +6638,17 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Serum, Plasma, DBS</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>DBS</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E249" t="n">
@@ -6663,17 +6663,17 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E250" t="n">
@@ -6688,17 +6688,17 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Were the patients in the study in a clinical trial?</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>NFLG, Envelope</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Envelope</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E251" t="n">
@@ -6713,17 +6713,17 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Were the patients in the study in a clinical trial?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NFLG, Envelope</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Envelope</t>
         </is>
       </c>
       <c r="E252" t="n">
@@ -6863,17 +6863,17 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Were sequences from the paper made publicly available?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>NRTI, NNRTI</t>
         </is>
       </c>
       <c r="E258" t="n">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI</t>
+          <t>Stavudine (d4T), Lamivudine (3TC), Zidovudine (AZT), Nevirapine (NVP), Efavirenz (EFV)</t>
         </is>
       </c>
       <c r="E259" t="n">
@@ -6913,17 +6913,17 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Were sequences from the paper made publicly available?</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Stavudine (d4T), Lamivudine (3TC), Zidovudine (AZT), Nevirapine (NVP), Efavirenz (EFV)</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E260" t="n">
@@ -7163,17 +7163,17 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>820 or 46</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E270" t="n">
@@ -7188,17 +7188,17 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>3TC, TDF, EFV, DTG, ATV</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E271" t="n">
@@ -7213,17 +7213,17 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>3TC, TDF, EFV, DTG, ATV</t>
+          <t>820 or 46</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>NNRTI, PI, INSTI</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E272" t="n">
@@ -7288,17 +7288,17 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Were samples cloned prior to sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Plasma, PBMC</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>PBMC</t>
         </is>
       </c>
       <c r="E275" t="n">
@@ -7313,17 +7313,17 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Plasma, PBMC</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>PBMC</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E276" t="n">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Were samples cloned prior to sequencing?</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -7413,17 +7413,17 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E280" t="n">
@@ -7438,17 +7438,17 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E281" t="n">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -7488,17 +7488,17 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>117</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E283" t="n">
@@ -7638,17 +7638,17 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>TDF, 3TC, DTG, ABC, LPV, ATV, EFV</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>Tenofovir, Lamivudine, Dolutegravir</t>
         </is>
       </c>
       <c r="E289" t="n">
@@ -7663,17 +7663,17 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>TDF, 3TC, DTG, ABC, LPV, ATV, EFV</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Tenofovir, Lamivudine, Dolutegravir</t>
+          <t>600</t>
         </is>
       </c>
       <c r="E290" t="n">
@@ -7713,17 +7713,17 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Does the paper report in vitro drug susceptibility data?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E292" t="n">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Protease, PR; Reverse transcriptase, RT</t>
+          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV)</t>
         </is>
       </c>
       <c r="E293" t="n">
@@ -7763,17 +7763,17 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Does the paper report in vitro drug susceptibility data?</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E294" t="n">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Abacavir (ABC), Zidovudine'(AZT), Zalcitabine (DDC), Didanosine (DDI), Lamivudine (3TC), Stavudine (D4T), Emtricitabine(FTC), Tenofovir (TFV), Nevirapine (NVP), Delavirdine (DLV), Efavirenz (EFV), Etravirine (ETR), Rilpivirine (RPV), Doravirine (DOR), Amprenavir (APV), Lopinavir'(LPV), Atazanavir (ATV), Derunavir (DRV), Nelfinavir (NFV)</t>
+          <t>Protease, PR; Reverse transcriptase, RT</t>
         </is>
       </c>
       <c r="E295" t="n">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>NNRTI</t>
         </is>
       </c>
       <c r="E301" t="n">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2015-2019</t>
+          <t>NVP</t>
         </is>
       </c>
       <c r="E302" t="n">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>NNRTI</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="E303" t="n">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>NVP</t>
+          <t>2015-2019</t>
         </is>
       </c>
       <c r="E304" t="n">
@@ -8063,17 +8063,17 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2020, 2022, 2023</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E306" t="n">
@@ -8088,17 +8088,17 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>PR, RT, IN</t>
+          <t>2020, 2022, 2023</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Integrase, IN</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E307" t="n">
@@ -8113,17 +8113,17 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>PR, RT, IN</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>Integrase, IN</t>
         </is>
       </c>
       <c r="E308" t="n">
@@ -8288,17 +8288,17 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>How many individuals had samples obtained for HIV sequencing?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>Plasma</t>
         </is>
       </c>
       <c r="E315" t="n">
@@ -8313,17 +8313,17 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E316" t="n">
@@ -8338,17 +8338,17 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Integrase, IN; Reverse transcriptase, RT; Protease, PR</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E317" t="n">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Plasma</t>
+          <t>INSTI; NRTI; NNRTI; PI</t>
         </is>
       </c>
       <c r="E318" t="n">
@@ -8388,17 +8388,17 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Dolutegravir (DTG); Raltegravir (RAL)</t>
         </is>
       </c>
       <c r="E319" t="n">
@@ -8413,17 +8413,17 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>How many individuals had samples obtained for HIV sequencing?</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E320" t="n">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>INSTI; NRTI; NNRTI; PI</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="E321" t="n">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Dolutegravir (DTG); Raltegravir (RAL)</t>
+          <t>Integrase, IN; Reverse transcriptase, RT; Protease, PR</t>
         </is>
       </c>
       <c r="E322" t="n">
@@ -8488,17 +8488,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E323" t="n">
@@ -8513,17 +8513,17 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2019-2020</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="E324" t="n">
@@ -8538,17 +8538,17 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Were any sequences obtained from individuals with virological failure on a treatment regimen?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>NRTI, NNRTI, PI, INSTI</t>
         </is>
       </c>
       <c r="E325" t="n">
@@ -8563,17 +8563,17 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Does the paper report HIV sequences from individuals who had previously received ARV drugs?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>AZT, TDF, XTC, EFV, NVP, LPV, DTG</t>
         </is>
       </c>
       <c r="E326" t="n">
@@ -8588,7 +8588,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI, INSTI</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="E327" t="n">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>AZT, TDF, XTC, EFV, NVP, LPV, DTG</t>
+          <t>2019-2020</t>
         </is>
       </c>
       <c r="E328" t="n">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>From which countries were the sequenced samples obtained?</t>
+          <t>What method was used for sequencing?</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>NGS</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E330" t="n">
@@ -8688,17 +8688,17 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>From what years were the sequenced samples obtained?</t>
+          <t>What type of samples were sequenced?</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2008-2019</t>
+          <t>Serum</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E331" t="n">
@@ -8713,17 +8713,17 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>What method was used for sequencing?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>NGS</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>NRTI, NNRTI, PI</t>
         </is>
       </c>
       <c r="E332" t="n">
@@ -8738,17 +8738,17 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>What type of samples were sequenced?</t>
+          <t>From which countries were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Serum</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E333" t="n">
@@ -8763,17 +8763,17 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>From what years were the sequenced samples obtained?</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>2008-2019</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>NRTI, NNRTI, PI</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="E334" t="n">
@@ -8788,17 +8788,17 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Which HIV genes were reported to have been sequenced?</t>
+          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Gag, Pol, Env, Nef, vpu</t>
+          <t>Not reported</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Envelope; Full genome; Near full length genome</t>
+          <t>INSTI, NRTI, NNRTI, PI, CAI</t>
         </is>
       </c>
       <c r="E335" t="n">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Which drug classes were received by individuals in the study before sample sequencing?</t>
+          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>INSTI, NRTI, NNRTI, PI, CAI</t>
+          <t>DTG, RAL, CAB, EFV, RPV, FTC, TFV, DRV, NFV, LEN</t>
         </is>
       </c>
       <c r="E336" t="n">
@@ -8838,17 +8838,17 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Which drugs were received by individuals in the study before sample sequencing?</t>
+          <t>Which HIV genes were reported to have been sequenced?</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Not reported</t>
+          <t>Gag, Pol, Env, Nef, vpu</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>DTG, RAL, CAB, EFV, RPV, FTC, TFV, DRV, NFV, LEN</t>
+          <t>Envelope; Full genome; Near full length genome</t>
         </is>
       </c>
       <c r="E337" t="n">
